--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1560,6 +1560,120 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127392591</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>536192</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6995397</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127352903</v>
+        <v>127352902</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,21 +1379,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536212</v>
+        <v>536192</v>
       </c>
       <c r="R9" t="n">
-        <v>6995419</v>
+        <v>6995397</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1465,35 +1465,51 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127352902</v>
+        <v>127392591</v>
       </c>
       <c r="B10" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Jönsodlingen, Jmt</t>
@@ -1506,7 +1522,7 @@
         <v>6995397</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1530,12 +1546,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1544,82 +1560,67 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127392591</v>
+        <v>127352903</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Jönsodlingen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536192</v>
+        <v>536212</v>
       </c>
       <c r="R11" t="n">
-        <v>6995397</v>
+        <v>6995419</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1643,12 +1644,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1657,19 +1658,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127352893</v>
       </c>
       <c r="B2" t="n">
-        <v>58516</v>
+        <v>58520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127352901</v>
       </c>
       <c r="B3" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127352896</v>
       </c>
       <c r="B4" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>127352900</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>127352904</v>
       </c>
       <c r="B6" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>127352899</v>
       </c>
       <c r="B7" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>127352895</v>
       </c>
       <c r="B8" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>127352902</v>
       </c>
       <c r="B9" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>127392591</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>127352903</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -1468,7 +1468,7 @@
         <v>127392591</v>
       </c>
       <c r="B10" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127352893</v>
       </c>
       <c r="B2" t="n">
-        <v>58520</v>
+        <v>58522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127352901</v>
       </c>
       <c r="B3" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127352896</v>
       </c>
       <c r="B4" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>127352900</v>
       </c>
       <c r="B5" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>127352904</v>
       </c>
       <c r="B6" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>127352899</v>
       </c>
       <c r="B7" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>127352895</v>
       </c>
       <c r="B8" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>127352902</v>
       </c>
       <c r="B9" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>127392591</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>127352903</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -1468,7 +1468,7 @@
         <v>127392591</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127352893</v>
       </c>
       <c r="B2" t="n">
-        <v>58522</v>
+        <v>58525</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127352901</v>
       </c>
       <c r="B3" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127352896</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>127352900</v>
       </c>
       <c r="B5" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>127352904</v>
       </c>
       <c r="B6" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>127352899</v>
       </c>
       <c r="B7" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>127352895</v>
       </c>
       <c r="B8" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>127352902</v>
       </c>
       <c r="B9" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>127392591</v>
       </c>
       <c r="B10" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>127352903</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127352893</v>
       </c>
       <c r="B2" t="n">
-        <v>58525</v>
+        <v>58531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127352901</v>
       </c>
       <c r="B3" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127352896</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>127352900</v>
       </c>
       <c r="B5" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>127352904</v>
       </c>
       <c r="B6" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>127352899</v>
       </c>
       <c r="B7" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>127352895</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>127352902</v>
       </c>
       <c r="B9" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>127392591</v>
       </c>
       <c r="B10" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>127352903</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -1468,7 +1468,7 @@
         <v>127392591</v>
       </c>
       <c r="B10" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -1468,7 +1468,7 @@
         <v>127392591</v>
       </c>
       <c r="B10" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -1468,7 +1468,7 @@
         <v>127392591</v>
       </c>
       <c r="B10" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127352893</v>
       </c>
       <c r="B2" t="n">
-        <v>58531</v>
+        <v>58544</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,6 +704,11 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jönsodlingen, Jmt</t>
@@ -754,6 +759,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -775,7 +781,7 @@
         <v>127352901</v>
       </c>
       <c r="B3" t="n">
-        <v>80132</v>
+        <v>80188</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +878,7 @@
         <v>127352896</v>
       </c>
       <c r="B4" t="n">
-        <v>57832</v>
+        <v>57845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +984,7 @@
         <v>127352900</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>80188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1081,7 @@
         <v>127352904</v>
       </c>
       <c r="B6" t="n">
-        <v>80132</v>
+        <v>80188</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1178,7 @@
         <v>127352899</v>
       </c>
       <c r="B7" t="n">
-        <v>80132</v>
+        <v>80188</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1275,7 @@
         <v>127352895</v>
       </c>
       <c r="B8" t="n">
-        <v>57669</v>
+        <v>57682</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,6 +1301,10 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Jönsodlingen, Jmt</t>
@@ -1371,7 +1381,7 @@
         <v>127352902</v>
       </c>
       <c r="B9" t="n">
-        <v>80132</v>
+        <v>80188</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1592,7 @@
         <v>127352903</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>57685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127352893</v>
       </c>
       <c r="B2" t="n">
-        <v>58544</v>
+        <v>58548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -766,12 +766,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -781,7 +781,7 @@
         <v>127352901</v>
       </c>
       <c r="B3" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -863,12 +863,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -878,7 +878,7 @@
         <v>127352896</v>
       </c>
       <c r="B4" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,12 +969,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -984,7 +984,7 @@
         <v>127352900</v>
       </c>
       <c r="B5" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,12 +1066,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
         <v>127352904</v>
       </c>
       <c r="B6" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,12 +1163,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1178,7 +1178,7 @@
         <v>127352899</v>
       </c>
       <c r="B7" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1275,7 +1275,7 @@
         <v>127352895</v>
       </c>
       <c r="B8" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,12 +1366,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
         <v>127352902</v>
       </c>
       <c r="B9" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,12 +1463,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1592,7 +1592,7 @@
         <v>127352903</v>
       </c>
       <c r="B11" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,12 +1674,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -781,7 +781,7 @@
         <v>127352901</v>
       </c>
       <c r="B3" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127352900</v>
       </c>
       <c r="B5" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>127352904</v>
       </c>
       <c r="B6" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>127352899</v>
       </c>
       <c r="B7" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>127352902</v>
       </c>
       <c r="B9" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127352893</v>
       </c>
       <c r="B2" t="n">
-        <v>58548</v>
+        <v>58575</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>127352901</v>
       </c>
       <c r="B3" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>127352896</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127352900</v>
       </c>
       <c r="B5" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>127352904</v>
       </c>
       <c r="B6" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>127352899</v>
       </c>
       <c r="B7" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>127352895</v>
       </c>
       <c r="B8" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>127352902</v>
       </c>
       <c r="B9" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>127352903</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -781,7 +781,7 @@
         <v>127352901</v>
       </c>
       <c r="B3" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127352900</v>
       </c>
       <c r="B5" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>127352904</v>
       </c>
       <c r="B6" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>127352899</v>
       </c>
       <c r="B7" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>127352902</v>
       </c>
       <c r="B9" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127352893</v>
       </c>
       <c r="B2" t="n">
-        <v>58575</v>
+        <v>58579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>127352901</v>
       </c>
       <c r="B3" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>127352896</v>
       </c>
       <c r="B4" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127352900</v>
       </c>
       <c r="B5" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>127352904</v>
       </c>
       <c r="B6" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>127352899</v>
       </c>
       <c r="B7" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>127352895</v>
       </c>
       <c r="B8" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>127352902</v>
       </c>
       <c r="B9" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>127352903</v>
       </c>
       <c r="B11" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127352893</v>
       </c>
       <c r="B2" t="n">
-        <v>58579</v>
+        <v>58582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>127352901</v>
       </c>
       <c r="B3" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>127352896</v>
       </c>
       <c r="B4" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127352900</v>
       </c>
       <c r="B5" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>127352904</v>
       </c>
       <c r="B6" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>127352899</v>
       </c>
       <c r="B7" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>127352895</v>
       </c>
       <c r="B8" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>127352902</v>
       </c>
       <c r="B9" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>127352903</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -781,7 +781,7 @@
         <v>127352901</v>
       </c>
       <c r="B3" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127352900</v>
       </c>
       <c r="B5" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>127352904</v>
       </c>
       <c r="B6" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>127352899</v>
       </c>
       <c r="B7" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>127352902</v>
       </c>
       <c r="B9" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -781,7 +781,7 @@
         <v>127352901</v>
       </c>
       <c r="B3" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127352900</v>
       </c>
       <c r="B5" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>127352904</v>
       </c>
       <c r="B6" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>127352899</v>
       </c>
       <c r="B7" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>127352902</v>
       </c>
       <c r="B9" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -878,7 +878,7 @@
         <v>127352896</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>58023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,6 +908,10 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Jönsodlingen, Jmt</t>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127352893</v>
+        <v>127352899</v>
       </c>
       <c r="B2" t="n">
-        <v>58582</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jönsodlingen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536240</v>
+        <v>536219</v>
       </c>
       <c r="R2" t="n">
-        <v>6995357</v>
+        <v>6995398</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -778,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127352901</v>
+        <v>127352900</v>
       </c>
       <c r="B3" t="n">
-        <v>80140</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536211</v>
+        <v>536207</v>
       </c>
       <c r="R3" t="n">
-        <v>6995383</v>
+        <v>6995372</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127352896</v>
+        <v>127352901</v>
       </c>
       <c r="B4" t="n">
-        <v>58043</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -886,45 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Jönsodlingen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536240</v>
+        <v>536211</v>
       </c>
       <c r="R4" t="n">
-        <v>6995357</v>
+        <v>6995383</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>stationär</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127352900</v>
+        <v>127352902</v>
       </c>
       <c r="B5" t="n">
-        <v>80140</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536207</v>
+        <v>536192</v>
       </c>
       <c r="R5" t="n">
-        <v>6995372</v>
+        <v>6995397</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1066,7 @@
         <v>127352904</v>
       </c>
       <c r="B6" t="n">
-        <v>80140</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,48 +1160,52 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127352899</v>
+        <v>127352895</v>
       </c>
       <c r="B7" t="n">
-        <v>80140</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Jönsodlingen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536219</v>
+        <v>536212</v>
       </c>
       <c r="R7" t="n">
-        <v>6995398</v>
+        <v>6995419</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1250,6 +1235,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hörde denna under tiden i området</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1276,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127352895</v>
+        <v>127352903</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1287,16 +1277,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1305,10 +1295,6 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Jönsodlingen, Jmt</t>
@@ -1351,11 +1337,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>hörde denna under tiden i området</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127352902</v>
+        <v>127352896</v>
       </c>
       <c r="B9" t="n">
-        <v>80140</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,37 +1374,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Jönsodlingen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536192</v>
+        <v>536240</v>
       </c>
       <c r="R9" t="n">
-        <v>6995397</v>
+        <v>6995357</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1453,6 +1442,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,50 +1473,39 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127392591</v>
+        <v>127352893</v>
       </c>
       <c r="B10" t="n">
-        <v>98470</v>
+        <v>58817</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1530,13 +1513,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536192</v>
+        <v>536240</v>
       </c>
       <c r="R10" t="n">
-        <v>6995397</v>
+        <v>6995357</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1560,12 +1543,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,60 +1564,76 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127352903</v>
+        <v>127392591</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Jönsodlingen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536212</v>
+        <v>536192</v>
       </c>
       <c r="R11" t="n">
-        <v>6995419</v>
+        <v>6995397</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1658,12 +1657,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1672,18 +1671,19 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 30637-2024 artfynd.xlsx
+++ b/artfynd/A 30637-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1160,52 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127352895</v>
+        <v>134506308</v>
       </c>
       <c r="B7" t="n">
-        <v>57950</v>
+        <v>80488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Jönsodlingen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536212</v>
+        <v>536172</v>
       </c>
       <c r="R7" t="n">
-        <v>6995419</v>
+        <v>6995426</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1229,17 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>hörde denna under tiden i området</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1266,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127352903</v>
+        <v>134506313</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>80488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536212</v>
+        <v>536171</v>
       </c>
       <c r="R8" t="n">
-        <v>6995419</v>
+        <v>6995394</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1331,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1363,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127352896</v>
+        <v>134506314</v>
       </c>
       <c r="B9" t="n">
-        <v>58114</v>
+        <v>80488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,45 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Jönsodlingen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536240</v>
+        <v>536155</v>
       </c>
       <c r="R9" t="n">
-        <v>6995357</v>
+        <v>6995415</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1436,17 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1473,53 +1451,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127352893</v>
+        <v>134506323</v>
       </c>
       <c r="B10" t="n">
-        <v>58817</v>
+        <v>80488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208249</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Jönsodlingen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536240</v>
+        <v>536133</v>
       </c>
       <c r="R10" t="n">
-        <v>6995357</v>
+        <v>6995427</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1543,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1557,7 +1530,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1576,50 +1548,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127392591</v>
+        <v>127352895</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1627,13 +1587,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536192</v>
+        <v>536212</v>
       </c>
       <c r="R11" t="n">
-        <v>6995397</v>
+        <v>6995419</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1657,12 +1617,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>hörde denna under tiden i området</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1671,22 +1636,2604 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127352903</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>536212</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6995419</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134506298</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>536207</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6995399</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134506299</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>536207</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6995417</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134506300</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>536212</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6995396</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134506301</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>536242</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6995401</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134506302</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>536224</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6995435</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134506304</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>536206</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6995429</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134506305</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>536197</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6995423</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134506306</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>536185</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6995437</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134506307</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>536172</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6995447</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134506309</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>536191</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6995386</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134506316</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>536235</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6995371</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134506310</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57816</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>536191</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6995382</v>
+      </c>
+      <c r="S24" t="n">
+        <v>50</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134506312</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>536274</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6995410</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127352896</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>536240</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6995357</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134506303</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>536234</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6995425</v>
+      </c>
+      <c r="S27" t="n">
+        <v>30</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134506311</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>536307</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6995326</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134506322</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>536137</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6995434</v>
+      </c>
+      <c r="S29" t="n">
+        <v>30</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127352893</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>536240</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6995357</v>
+      </c>
+      <c r="S30" t="n">
+        <v>50</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127392591</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>536192</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6995397</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
           <t>Maria Danvind</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>Maria Danvind</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134506315</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>536141</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6995442</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134506317</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>536188</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6995376</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134506318</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>536191</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6995395</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134506319</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>536202</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6995420</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134506320</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Jönsoldingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>536186</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6995427</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134506321</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Jönsodlingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>536190</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6995407</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
